--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_github_projects\lanupro_vocabulary_2025\data\raw_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C484D384-E271-4D9E-AF40-BBF81A92C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223CBDE0-158A-4006-9ED3-E20C3F9DAC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="274">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -432,6 +432,435 @@
   </si>
   <si>
     <t>levels if the variable is a factor (in wide format)</t>
+  </si>
+  <si>
+    <t>c04_0</t>
+  </si>
+  <si>
+    <t>c05_0</t>
+  </si>
+  <si>
+    <t>c06_0</t>
+  </si>
+  <si>
+    <t>c07_0</t>
+  </si>
+  <si>
+    <t>c08_0</t>
+  </si>
+  <si>
+    <t>c09_0</t>
+  </si>
+  <si>
+    <t>c10_0</t>
+  </si>
+  <si>
+    <t>c10_1</t>
+  </si>
+  <si>
+    <t>c11_0</t>
+  </si>
+  <si>
+    <t>c12_0</t>
+  </si>
+  <si>
+    <t>c13_0</t>
+  </si>
+  <si>
+    <t>c12_1</t>
+  </si>
+  <si>
+    <t>iso_c14_0</t>
+  </si>
+  <si>
+    <t>c14_0</t>
+  </si>
+  <si>
+    <t>iso_c15_0</t>
+  </si>
+  <si>
+    <t>anteiso_c15_0</t>
+  </si>
+  <si>
+    <t>c14_1</t>
+  </si>
+  <si>
+    <t>c15_0</t>
+  </si>
+  <si>
+    <t>iso_c16_0</t>
+  </si>
+  <si>
+    <t>c16_0</t>
+  </si>
+  <si>
+    <t>trans_6_plus_trans_7_plus_trans_8_c16_1</t>
+  </si>
+  <si>
+    <t>trans_9_c16_1</t>
+  </si>
+  <si>
+    <t>trans_10_c16_1</t>
+  </si>
+  <si>
+    <t>trans_11_plus_trans_12_c16_1</t>
+  </si>
+  <si>
+    <t>iso_c17_0</t>
+  </si>
+  <si>
+    <t>cis_7_c16_1</t>
+  </si>
+  <si>
+    <t>cis_9_c16_1</t>
+  </si>
+  <si>
+    <t>anteiso_c17_0</t>
+  </si>
+  <si>
+    <t>cis_11_c16_1</t>
+  </si>
+  <si>
+    <t>trans_14_c16_1</t>
+  </si>
+  <si>
+    <t>cis_13_c16_1</t>
+  </si>
+  <si>
+    <t>c17_0</t>
+  </si>
+  <si>
+    <t>iso_c17_0_plus_cis_7_plus_trans_11_plus_trans_12_c16_1</t>
+  </si>
+  <si>
+    <t>cis_9_c17_1</t>
+  </si>
+  <si>
+    <t>iso_c18_0</t>
+  </si>
+  <si>
+    <t>trans_6_plus_trans_7_plus_trans_8_c18_1</t>
+  </si>
+  <si>
+    <t>trans_9_c18_1</t>
+  </si>
+  <si>
+    <t>trans_10_c18_1</t>
+  </si>
+  <si>
+    <t>trans_11_c18_1</t>
+  </si>
+  <si>
+    <t>trans_12_c18_1</t>
+  </si>
+  <si>
+    <t>cis_9_plus_trans_13_plus_trans_14_c18_1</t>
+  </si>
+  <si>
+    <t>cis_9_plus_trans_12_plus_13_plus_trans_14_c18_1</t>
+  </si>
+  <si>
+    <t>trans_15_c18_1</t>
+  </si>
+  <si>
+    <t>cis_11_c18_1</t>
+  </si>
+  <si>
+    <t>cis_12_c18_1</t>
+  </si>
+  <si>
+    <t>cis_13_c18_1</t>
+  </si>
+  <si>
+    <t>cis_14_plus_trans_16_c18_1</t>
+  </si>
+  <si>
+    <t>cis_15_c18_1</t>
+  </si>
+  <si>
+    <t>cla_cis_9_trans_11_c18_2</t>
+  </si>
+  <si>
+    <t>trans_11_cis_15_c18_2</t>
+  </si>
+  <si>
+    <t>n_6_c18_2</t>
+  </si>
+  <si>
+    <t>n_6_c18_3</t>
+  </si>
+  <si>
+    <t>c20_0</t>
+  </si>
+  <si>
+    <t>n_3_c18_3</t>
+  </si>
+  <si>
+    <t>cis_7_c20_1</t>
+  </si>
+  <si>
+    <t>cis_9_c20_1</t>
+  </si>
+  <si>
+    <t>cla_trans_10_cis_12_c18_2</t>
+  </si>
+  <si>
+    <t>cis_7_plus_cis_9_c20_1_plus_cla_cis_9_trans_11_c18_2</t>
+  </si>
+  <si>
+    <t>cis_7_c20_1_plus_cla_cis_9_trans_11_c18_2</t>
+  </si>
+  <si>
+    <t>n_6_c20_3</t>
+  </si>
+  <si>
+    <t>c22_0</t>
+  </si>
+  <si>
+    <t>n_3_c20_3</t>
+  </si>
+  <si>
+    <t>n_6_c20_4</t>
+  </si>
+  <si>
+    <t>n_3_c20_5</t>
+  </si>
+  <si>
+    <t>n_6_c22_4</t>
+  </si>
+  <si>
+    <t>n_6_c22_5</t>
+  </si>
+  <si>
+    <t>n_3_c22_5</t>
+  </si>
+  <si>
+    <t>n_3_c22_6</t>
+  </si>
+  <si>
+    <t>sfa</t>
+  </si>
+  <si>
+    <t>SFA</t>
+  </si>
+  <si>
+    <t>mufa</t>
+  </si>
+  <si>
+    <t>MUFA</t>
+  </si>
+  <si>
+    <t>pufa</t>
+  </si>
+  <si>
+    <t>PUFA</t>
+  </si>
+  <si>
+    <t>C4:0</t>
+  </si>
+  <si>
+    <t>C5:0</t>
+  </si>
+  <si>
+    <t>C6:0</t>
+  </si>
+  <si>
+    <t>C7:0</t>
+  </si>
+  <si>
+    <t>C8:0</t>
+  </si>
+  <si>
+    <t>C9:0</t>
+  </si>
+  <si>
+    <t>C10:0</t>
+  </si>
+  <si>
+    <t>C10:1</t>
+  </si>
+  <si>
+    <t>C11:0</t>
+  </si>
+  <si>
+    <t>C12:0</t>
+  </si>
+  <si>
+    <t>C12:1</t>
+  </si>
+  <si>
+    <t>C13:0</t>
+  </si>
+  <si>
+    <t>iso-C14:0</t>
+  </si>
+  <si>
+    <t>C14:0</t>
+  </si>
+  <si>
+    <t>C14:1</t>
+  </si>
+  <si>
+    <t>iso-C15:0</t>
+  </si>
+  <si>
+    <t>anteiso-C15:0</t>
+  </si>
+  <si>
+    <t>C15:0</t>
+  </si>
+  <si>
+    <t>iso-C16:0</t>
+  </si>
+  <si>
+    <t>C16:0</t>
+  </si>
+  <si>
+    <t>t6/7/8-C16:1</t>
+  </si>
+  <si>
+    <t>t9-C16:1</t>
+  </si>
+  <si>
+    <t>t10-C16:1</t>
+  </si>
+  <si>
+    <t>t11/12-C16:1</t>
+  </si>
+  <si>
+    <t>c7-C16:1</t>
+  </si>
+  <si>
+    <t>c9-C16:1</t>
+  </si>
+  <si>
+    <t>c11-C16:1</t>
+  </si>
+  <si>
+    <t>t14-C16:1</t>
+  </si>
+  <si>
+    <t>c13-C16:1</t>
+  </si>
+  <si>
+    <t>C17:0</t>
+  </si>
+  <si>
+    <t>iso-C17:0</t>
+  </si>
+  <si>
+    <t>anteiso-C17:0</t>
+  </si>
+  <si>
+    <t>iso-C17:0 + C16:1</t>
+  </si>
+  <si>
+    <t>c9-C17:1</t>
+  </si>
+  <si>
+    <t>C18:0</t>
+  </si>
+  <si>
+    <t>iso-C18:0</t>
+  </si>
+  <si>
+    <t>t6/7/8-C18:1</t>
+  </si>
+  <si>
+    <t>t9-C18:1</t>
+  </si>
+  <si>
+    <t>t10-C18:1</t>
+  </si>
+  <si>
+    <t>t11-C18:1</t>
+  </si>
+  <si>
+    <t>t12-C18:1</t>
+  </si>
+  <si>
+    <t>c9/t13/14-C18:1</t>
+  </si>
+  <si>
+    <t>c9/t12/13/14-C18:1</t>
+  </si>
+  <si>
+    <t>t15-C18:1</t>
+  </si>
+  <si>
+    <t>c11-C18:1</t>
+  </si>
+  <si>
+    <t>c12-C18:1</t>
+  </si>
+  <si>
+    <t>c13-C18:1</t>
+  </si>
+  <si>
+    <t>c14/t16-C18:1</t>
+  </si>
+  <si>
+    <t>c15-C18:1</t>
+  </si>
+  <si>
+    <t>CLA (c9,t11)</t>
+  </si>
+  <si>
+    <t>t11,c15-C18:2</t>
+  </si>
+  <si>
+    <t>C20:0</t>
+  </si>
+  <si>
+    <t>c7-C20:1</t>
+  </si>
+  <si>
+    <t>c9-C20:1</t>
+  </si>
+  <si>
+    <t>CLA (t10,c12)</t>
+  </si>
+  <si>
+    <t>C20:1 + CLA</t>
+  </si>
+  <si>
+    <t>C22:0</t>
+  </si>
+  <si>
+    <t>C18:2n-6</t>
+  </si>
+  <si>
+    <t>C18:3n-6</t>
+  </si>
+  <si>
+    <t>C18:3n-3</t>
+  </si>
+  <si>
+    <t>C20:3n-6</t>
+  </si>
+  <si>
+    <t>C20:3n-3</t>
+  </si>
+  <si>
+    <t>C20:4n-6</t>
+  </si>
+  <si>
+    <t>C20:5n-3</t>
+  </si>
+  <si>
+    <t>C22:4n-6</t>
+  </si>
+  <si>
+    <t>C22:5n-6</t>
+  </si>
+  <si>
+    <t>C22:5n-3</t>
+  </si>
+  <si>
+    <t>C22:6n-3</t>
+  </si>
+  <si>
+    <t>figure_table_label</t>
   </si>
 </sst>
 </file>
@@ -1714,26 +2143,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE468F5-6397-4C82-931F-B2CE02F46428}">
-  <dimension ref="A1:DD2"/>
+  <dimension ref="A1:DE74"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:108">
+    <row r="1" spans="1:109">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1741,325 +2171,328 @@
         <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:108">
+    <row r="2" spans="1:109">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2067,22 +2500,817 @@
         <v>118</v>
       </c>
       <c r="C2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" t="s">
         <v>119</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>120</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>110</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:109">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:109">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:109">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:109">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:109">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:109">
+      <c r="A8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:109">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:109">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:109">
+      <c r="A11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:109">
+      <c r="A12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:109">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:109">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:109">
+      <c r="A15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:109">
+      <c r="A16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C25" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>172</v>
+      </c>
+      <c r="B45" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" t="s">
+        <v>248</v>
+      </c>
+      <c r="C46" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>175</v>
+      </c>
+      <c r="B48" t="s">
+        <v>250</v>
+      </c>
+      <c r="C48" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C49" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" t="s">
+        <v>253</v>
+      </c>
+      <c r="C51" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C52" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>180</v>
+      </c>
+      <c r="B53" t="s">
+        <v>255</v>
+      </c>
+      <c r="C53" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" t="s">
+        <v>262</v>
+      </c>
+      <c r="C54" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" t="s">
+        <v>264</v>
+      </c>
+      <c r="C56" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>183</v>
+      </c>
+      <c r="B57" t="s">
+        <v>256</v>
+      </c>
+      <c r="C57" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" t="s">
+        <v>257</v>
+      </c>
+      <c r="C58" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" t="s">
+        <v>259</v>
+      </c>
+      <c r="C60" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>188</v>
+      </c>
+      <c r="B61" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>190</v>
+      </c>
+      <c r="B63" t="s">
+        <v>265</v>
+      </c>
+      <c r="C63" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>192</v>
+      </c>
+      <c r="B64" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" t="s">
+        <v>268</v>
+      </c>
+      <c r="C66" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>191</v>
+      </c>
+      <c r="B67" t="s">
+        <v>261</v>
+      </c>
+      <c r="C67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>196</v>
+      </c>
+      <c r="B69" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" t="s">
+        <v>271</v>
+      </c>
+      <c r="C70" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>272</v>
+      </c>
+      <c r="C71" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" t="s">
+        <v>200</v>
+      </c>
+      <c r="C72" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>201</v>
+      </c>
+      <c r="B73" t="s">
+        <v>202</v>
+      </c>
+      <c r="C73" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>203</v>
+      </c>
+      <c r="B74" t="s">
+        <v>204</v>
+      </c>
+      <c r="C74" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2095,13 +3323,13 @@
           <x14:formula1>
             <xm:f>description!$E$7:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
+          <xm:sqref>G2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{63FF082E-FE70-4372-A8CC-717DC18F28AE}">
           <x14:formula1>
             <xm:f>description!$E$6:$H$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2</xm:sqref>
+          <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223CBDE0-158A-4006-9ED3-E20C3F9DAC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BF523-05CF-49BD-9998-9492CDF6EFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="342">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -391,9 +391,6 @@
   </si>
   <si>
     <t>atol_ontology_sample_type_meat</t>
-  </si>
-  <si>
-    <t>C18:0, C18.0</t>
   </si>
   <si>
     <t>ATOL_0000650</t>
@@ -861,6 +858,213 @@
   </si>
   <si>
     <t>figure_table_label</t>
+  </si>
+  <si>
+    <t>C4:0, 04:0, 4:0</t>
+  </si>
+  <si>
+    <t>C5:0, 05:0, 5:0</t>
+  </si>
+  <si>
+    <t>C6:0, 06:0, 6:0</t>
+  </si>
+  <si>
+    <t>C18:0, C18.0, 18:0</t>
+  </si>
+  <si>
+    <t>C7:0, 07:0, 7:0</t>
+  </si>
+  <si>
+    <t>C8:0, 08:0, 8:0</t>
+  </si>
+  <si>
+    <t>C9:0, 09:0, 9:0</t>
+  </si>
+  <si>
+    <t>C10:0, 10:0</t>
+  </si>
+  <si>
+    <t>C10:1, 10:1</t>
+  </si>
+  <si>
+    <t>C11:0, 11:0</t>
+  </si>
+  <si>
+    <t>C12:0, 12:0</t>
+  </si>
+  <si>
+    <t>C12:1, 12:1</t>
+  </si>
+  <si>
+    <t>C13:0, 13:0</t>
+  </si>
+  <si>
+    <t>iso-C14:0, iso-C14.0, iso14:0</t>
+  </si>
+  <si>
+    <t>C14:0, C14.0, 14:0</t>
+  </si>
+  <si>
+    <t>C14:1, 14:1</t>
+  </si>
+  <si>
+    <t>iso-C15:0, iso-C15.0, iso15:0</t>
+  </si>
+  <si>
+    <t>anteiso-C15:0, anteiso-C15.0, anteiso15:0</t>
+  </si>
+  <si>
+    <t>C15:0, C15.0, 15:0</t>
+  </si>
+  <si>
+    <t>iso-C16:0, iso-C16.0</t>
+  </si>
+  <si>
+    <t>C16:0, C16.0, 16:0</t>
+  </si>
+  <si>
+    <t>t6/7/8-C16:1, trans-6/7/8-C16:1, t6/7/8C16:1</t>
+  </si>
+  <si>
+    <t>t9-C16:1, trans-9-C16:1, t9C16:1</t>
+  </si>
+  <si>
+    <t>t10-C16:1, trans-10-C16:1, t10C16:1</t>
+  </si>
+  <si>
+    <t>t11/12-C16:1, trans-11/12-C16:1, t11/12C16:1</t>
+  </si>
+  <si>
+    <t>c7-C16:1, cis-7-C16:1, c716:1</t>
+  </si>
+  <si>
+    <t>c9-C16:1, cis-9-C16:1, c9C16:1</t>
+  </si>
+  <si>
+    <t>c11-C16:1, cis-11-C16:1, c11C16:1</t>
+  </si>
+  <si>
+    <t>t14-C16:1, trans-14-C16:1, t14C16:1</t>
+  </si>
+  <si>
+    <t>c13-C16:1, cis-13-C16:1, c13C16:1</t>
+  </si>
+  <si>
+    <t>C17:0, C17.0, 17:0</t>
+  </si>
+  <si>
+    <t>iso-C17:0, iso-C17.0, iso17:0</t>
+  </si>
+  <si>
+    <t>anteiso-C17:0, anteiso-C17.0, antiso17:0</t>
+  </si>
+  <si>
+    <t>c9-C17:1, cis-9-C17:1, c917:1</t>
+  </si>
+  <si>
+    <t>iso-C18:0, iso-C18.0, isoC18:0</t>
+  </si>
+  <si>
+    <t>t6/7/8-C18:1, trans-6/7/8-C18:1, t6/7/818:1</t>
+  </si>
+  <si>
+    <t>t9-C18:1, trans-9-C18:1, t918:1</t>
+  </si>
+  <si>
+    <t>t10-C18:1, trans-10-C18:1, t1018:1</t>
+  </si>
+  <si>
+    <t>t11-C18:1, trans-11-C18:1, t1118:1</t>
+  </si>
+  <si>
+    <t>t12-C18:1, trans-12-C18:1, t12C18:1</t>
+  </si>
+  <si>
+    <t>c9/t13/14-C18:1, cis-9/trans-13/trans-14-C18:1, t13/14+c918:1</t>
+  </si>
+  <si>
+    <t>c9/t12/13/14-C18:1, cis-9/trans-12/13/14-C18:1</t>
+  </si>
+  <si>
+    <t>t15-C18:1, trans-15-C18:1, t1518:1</t>
+  </si>
+  <si>
+    <t>c11-C18:1, cis-11-C18:1, c1118:1</t>
+  </si>
+  <si>
+    <t>c12-C18:1, cis-12-C18:1, c1218:1</t>
+  </si>
+  <si>
+    <t>c13-C18:1, cis-13-C18:1, c1318:1</t>
+  </si>
+  <si>
+    <t>c14/t16-C18:1, cis-14/trans-16-C18:1, c14+t1618:1</t>
+  </si>
+  <si>
+    <t>c15-C18:1, cis-15-C18:1, c1518:1</t>
+  </si>
+  <si>
+    <t>CLA (c9,t11), CLA c9,t11, cis-9 trans-11 CLA, CLAc9t1118:2</t>
+  </si>
+  <si>
+    <t>t11,c15-C18:2, trans-11 cis-15-C18:2, t11c1518:2</t>
+  </si>
+  <si>
+    <t>C18:2n-6, C18:2 n-6, 18:2n-6, 18:2 n-6</t>
+  </si>
+  <si>
+    <t>C18:3n-6, C18:3 n-6, 18:3n-6, 18:3 n-6, n-618:3</t>
+  </si>
+  <si>
+    <t>C18:3n-3, C18:3 n-3, 18:3n-3, 18:3 n-3, n-318:3</t>
+  </si>
+  <si>
+    <t>C20:0, C20.0, 20:0</t>
+  </si>
+  <si>
+    <t>c7-C20:1, cis-7-C20:1</t>
+  </si>
+  <si>
+    <t>c9-C20:1, cis-9-C20:1, c920:1</t>
+  </si>
+  <si>
+    <t>CLA (t10,c12), CLA t10,c12, trans-10 cis-12 CLA, CLAt10c1218:2</t>
+  </si>
+  <si>
+    <t>C20:3n-6, C20:3 n-6, 20:3n-6, 20:3 n-6, n-620:3</t>
+  </si>
+  <si>
+    <t>C20:3n-3, C20:3 n-3, 20:3n-3, 20:3 n-3, n-320:3</t>
+  </si>
+  <si>
+    <t>C20:4n-6, C20:4 n-6, 20:4n-6, 20:4 n-6, n-620:4</t>
+  </si>
+  <si>
+    <t>C20:5n-3, C20:5 n-3, 20:5n-3, 20:5 n-3, n-3C20:5</t>
+  </si>
+  <si>
+    <t>C22:0, C22.0, 22:0</t>
+  </si>
+  <si>
+    <t>C22:4n-6, C22:4 n-6, 22:4n-6, 22:4 n-6, n-622:4</t>
+  </si>
+  <si>
+    <t>C22:5n-6, C22:5 n-6, 22:5n-6, 22:5 n-6, n-622:5</t>
+  </si>
+  <si>
+    <t>C22:5n-3, C22:5 n-3, 22:5n-3, 22:5 n-3, n-322:5</t>
+  </si>
+  <si>
+    <t>C22:6n-3, C22:6 n-3, 22:6n-3, 22:6 n-3, n-322:6</t>
+  </si>
+  <si>
+    <t>SFA, saturated fatty acids</t>
+  </si>
+  <si>
+    <t>MUFA, monounsaturated fatty acids</t>
+  </si>
+  <si>
+    <t>PUFA, polyunsaturated fatty acids</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2375,7 @@
         <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>116</v>
@@ -2497,16 +2701,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" t="s">
         <v>118</v>
       </c>
-      <c r="C2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>119</v>
-      </c>
-      <c r="E2" t="s">
-        <v>120</v>
       </c>
       <c r="F2" t="s">
         <v>110</v>
@@ -2523,376 +2727,376 @@
     </row>
     <row r="3" spans="1:109">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:109">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:109">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:109">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:109">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:109">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:109">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:109">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:109">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:109">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:109">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="C13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:109">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:109">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:109">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="C16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>229</v>
+        <v>298</v>
       </c>
       <c r="C27" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="C28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s">
-        <v>232</v>
+        <v>301</v>
       </c>
       <c r="C30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="C31" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="C32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="C33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="C34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B36" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="C36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2900,417 +3104,417 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="C37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B39" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="C40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="C41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="C43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B44" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="C44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B45" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="C45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B46" t="s">
-        <v>248</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B47" t="s">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="C47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
       <c r="C48" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>318</v>
       </c>
       <c r="C49" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="C51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" t="s">
-        <v>254</v>
+        <v>321</v>
       </c>
       <c r="C52" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="C54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="C57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B58" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="C59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B60" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="C60" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B63" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="C63" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B64" t="s">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>267</v>
+        <v>332</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B66" t="s">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B67" t="s">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="C67" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B68" t="s">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="C68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B69" t="s">
-        <v>270</v>
+        <v>336</v>
       </c>
       <c r="C69" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B70" t="s">
-        <v>271</v>
+        <v>337</v>
       </c>
       <c r="C70" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="C71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>198</v>
+      </c>
+      <c r="B72" t="s">
+        <v>339</v>
+      </c>
+      <c r="C72" t="s">
         <v>199</v>
-      </c>
-      <c r="B72" t="s">
-        <v>200</v>
-      </c>
-      <c r="C72" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>200</v>
+      </c>
+      <c r="B73" t="s">
+        <v>340</v>
+      </c>
+      <c r="C73" t="s">
         <v>201</v>
-      </c>
-      <c r="B73" t="s">
-        <v>202</v>
-      </c>
-      <c r="C73" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
+        <v>202</v>
+      </c>
+      <c r="B74" t="s">
+        <v>341</v>
+      </c>
+      <c r="C74" t="s">
         <v>203</v>
-      </c>
-      <c r="B74" t="s">
-        <v>204</v>
-      </c>
-      <c r="C74" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -3385,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3399,7 +3603,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="57.6">
@@ -3413,7 +3617,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="57.6">
@@ -3427,7 +3631,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3441,7 +3645,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
         <v>109</v>
@@ -3467,7 +3671,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -3487,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3501,12 +3705,12 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -3515,7 +3719,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BF523-05CF-49BD-9998-9492CDF6EFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943AA0AF-A399-4B96-AC52-B734344EA122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="345">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -884,187 +884,196 @@
     <t>C10:0, 10:0</t>
   </si>
   <si>
-    <t>C10:1, 10:1</t>
-  </si>
-  <si>
     <t>C11:0, 11:0</t>
   </si>
   <si>
     <t>C12:0, 12:0</t>
   </si>
   <si>
-    <t>C12:1, 12:1</t>
-  </si>
-  <si>
     <t>C13:0, 13:0</t>
   </si>
   <si>
-    <t>iso-C14:0, iso-C14.0, iso14:0</t>
-  </si>
-  <si>
     <t>C14:0, C14.0, 14:0</t>
   </si>
   <si>
-    <t>C14:1, 14:1</t>
-  </si>
-  <si>
-    <t>iso-C15:0, iso-C15.0, iso15:0</t>
-  </si>
-  <si>
-    <t>anteiso-C15:0, anteiso-C15.0, anteiso15:0</t>
-  </si>
-  <si>
     <t>C15:0, C15.0, 15:0</t>
   </si>
   <si>
-    <t>iso-C16:0, iso-C16.0</t>
-  </si>
-  <si>
     <t>C16:0, C16.0, 16:0</t>
   </si>
   <si>
-    <t>t6/7/8-C16:1, trans-6/7/8-C16:1, t6/7/8C16:1</t>
-  </si>
-  <si>
-    <t>t9-C16:1, trans-9-C16:1, t9C16:1</t>
-  </si>
-  <si>
-    <t>t10-C16:1, trans-10-C16:1, t10C16:1</t>
-  </si>
-  <si>
-    <t>t11/12-C16:1, trans-11/12-C16:1, t11/12C16:1</t>
-  </si>
-  <si>
-    <t>c7-C16:1, cis-7-C16:1, c716:1</t>
-  </si>
-  <si>
-    <t>c9-C16:1, cis-9-C16:1, c9C16:1</t>
-  </si>
-  <si>
-    <t>c11-C16:1, cis-11-C16:1, c11C16:1</t>
-  </si>
-  <si>
-    <t>t14-C16:1, trans-14-C16:1, t14C16:1</t>
-  </si>
-  <si>
-    <t>c13-C16:1, cis-13-C16:1, c13C16:1</t>
-  </si>
-  <si>
     <t>C17:0, C17.0, 17:0</t>
   </si>
   <si>
-    <t>iso-C17:0, iso-C17.0, iso17:0</t>
-  </si>
-  <si>
-    <t>anteiso-C17:0, anteiso-C17.0, antiso17:0</t>
-  </si>
-  <si>
-    <t>c9-C17:1, cis-9-C17:1, c917:1</t>
-  </si>
-  <si>
-    <t>iso-C18:0, iso-C18.0, isoC18:0</t>
-  </si>
-  <si>
-    <t>t6/7/8-C18:1, trans-6/7/8-C18:1, t6/7/818:1</t>
-  </si>
-  <si>
-    <t>t9-C18:1, trans-9-C18:1, t918:1</t>
-  </si>
-  <si>
-    <t>t10-C18:1, trans-10-C18:1, t1018:1</t>
-  </si>
-  <si>
-    <t>t11-C18:1, trans-11-C18:1, t1118:1</t>
-  </si>
-  <si>
-    <t>t12-C18:1, trans-12-C18:1, t12C18:1</t>
-  </si>
-  <si>
-    <t>c9/t13/14-C18:1, cis-9/trans-13/trans-14-C18:1, t13/14+c918:1</t>
-  </si>
-  <si>
-    <t>c9/t12/13/14-C18:1, cis-9/trans-12/13/14-C18:1</t>
-  </si>
-  <si>
-    <t>t15-C18:1, trans-15-C18:1, t1518:1</t>
-  </si>
-  <si>
-    <t>c11-C18:1, cis-11-C18:1, c1118:1</t>
-  </si>
-  <si>
-    <t>c12-C18:1, cis-12-C18:1, c1218:1</t>
-  </si>
-  <si>
-    <t>c13-C18:1, cis-13-C18:1, c1318:1</t>
-  </si>
-  <si>
-    <t>c14/t16-C18:1, cis-14/trans-16-C18:1, c14+t1618:1</t>
-  </si>
-  <si>
-    <t>c15-C18:1, cis-15-C18:1, c1518:1</t>
-  </si>
-  <si>
-    <t>CLA (c9,t11), CLA c9,t11, cis-9 trans-11 CLA, CLAc9t1118:2</t>
-  </si>
-  <si>
-    <t>t11,c15-C18:2, trans-11 cis-15-C18:2, t11c1518:2</t>
-  </si>
-  <si>
-    <t>C18:2n-6, C18:2 n-6, 18:2n-6, 18:2 n-6</t>
-  </si>
-  <si>
-    <t>C18:3n-6, C18:3 n-6, 18:3n-6, 18:3 n-6, n-618:3</t>
-  </si>
-  <si>
-    <t>C18:3n-3, C18:3 n-3, 18:3n-3, 18:3 n-3, n-318:3</t>
-  </si>
-  <si>
     <t>C20:0, C20.0, 20:0</t>
   </si>
   <si>
-    <t>c7-C20:1, cis-7-C20:1</t>
-  </si>
-  <si>
-    <t>c9-C20:1, cis-9-C20:1, c920:1</t>
-  </si>
-  <si>
-    <t>CLA (t10,c12), CLA t10,c12, trans-10 cis-12 CLA, CLAt10c1218:2</t>
-  </si>
-  <si>
-    <t>C20:3n-6, C20:3 n-6, 20:3n-6, 20:3 n-6, n-620:3</t>
-  </si>
-  <si>
-    <t>C20:3n-3, C20:3 n-3, 20:3n-3, 20:3 n-3, n-320:3</t>
-  </si>
-  <si>
-    <t>C20:4n-6, C20:4 n-6, 20:4n-6, 20:4 n-6, n-620:4</t>
-  </si>
-  <si>
-    <t>C20:5n-3, C20:5 n-3, 20:5n-3, 20:5 n-3, n-3C20:5</t>
-  </si>
-  <si>
     <t>C22:0, C22.0, 22:0</t>
   </si>
   <si>
-    <t>C22:4n-6, C22:4 n-6, 22:4n-6, 22:4 n-6, n-622:4</t>
-  </si>
-  <si>
-    <t>C22:5n-6, C22:5 n-6, 22:5n-6, 22:5 n-6, n-622:5</t>
-  </si>
-  <si>
-    <t>C22:5n-3, C22:5 n-3, 22:5n-3, 22:5 n-3, n-322:5</t>
-  </si>
-  <si>
-    <t>C22:6n-3, C22:6 n-3, 22:6n-3, 22:6 n-3, n-322:6</t>
-  </si>
-  <si>
-    <t>SFA, saturated fatty acids</t>
-  </si>
-  <si>
-    <t>MUFA, monounsaturated fatty acids</t>
-  </si>
-  <si>
-    <t>PUFA, polyunsaturated fatty acids</t>
+    <t>C10:1, 10:1, C10.1</t>
+  </si>
+  <si>
+    <t>C12:1, 12:1, C12.1</t>
+  </si>
+  <si>
+    <t>iso-C14:0, iso-C14.0, iso14:0, iso-14:0</t>
+  </si>
+  <si>
+    <t>C14:1, 14:1, C14.1</t>
+  </si>
+  <si>
+    <t>iso-C15:0, iso-C15.0, iso15:0, iso-15:0</t>
+  </si>
+  <si>
+    <t>anteiso-C15:0, anteiso-C15.0, anteiso15:0, anteiso-15:0</t>
+  </si>
+  <si>
+    <t>iso-C16:0, iso-C16.0, iso16:0, iso-16:0, isoC16:0</t>
+  </si>
+  <si>
+    <t>t6/7/8-C16:1, trans-6/7/8-C16:1, t6/7/8C16:1, t6/7/8 16:1, trans6/7/8-C16:1</t>
+  </si>
+  <si>
+    <t>t9-C16:1, trans-9-C16:1, t9C16:1, t9 16:1, trans9-C16:1</t>
+  </si>
+  <si>
+    <t>t10-C16:1, trans-10-C16:1, t10C16:1, t10 16:1, trans10-C16:1</t>
+  </si>
+  <si>
+    <t>t11/12-C16:1, trans-11/12-C16:1, t11/12C16:1, t11/t12 16:1, t11/12 16:1</t>
+  </si>
+  <si>
+    <t>c7-C16:1, cis-7-C16:1, c7C16:1, c716:1, c7 16:1</t>
+  </si>
+  <si>
+    <t>c9-C16:1, cis-9-C16:1, c9C16:1, c916:1, c9 16:1</t>
+  </si>
+  <si>
+    <t>c11-C16:1, cis-11-C16:1, c11C16:1, c1116:1, c11 16:1</t>
+  </si>
+  <si>
+    <t>t14-C16:1, trans-14-C16:1, t14C16:1, t1416:1, t14 16:1</t>
+  </si>
+  <si>
+    <t>c13-C16:1, cis-13-C16:1, c13C16:1, c1316:1, c13 16:1</t>
+  </si>
+  <si>
+    <t>iso-C17:0, iso-C17.0, isoC17:0, iso17:0, iso-17:0, iso 17:0</t>
+  </si>
+  <si>
+    <t>anteiso-C17:0, anteiso-C17.0, anteisoC17:0, anteiso17:0, anteiso-17:0, anteiso 17:0, antiso17:0</t>
+  </si>
+  <si>
+    <t>iso-C17:0 + C16:1, iso-C17:0+C16:1, iso17:0+C16:1, iso 17:0 + c7/t11/12 16:1</t>
+  </si>
+  <si>
+    <t>c9-C17:1, cis-9-C17:1, c9C17:1, c917:1, c9 17:1</t>
+  </si>
+  <si>
+    <t>iso-C18:0, iso-C18.0, isoC18:0, iso18:0, iso-18:0, iso 18:0</t>
+  </si>
+  <si>
+    <t>t6/7/8-C18:1, trans-6/7/8-C18:1, t6/7/8C18:1, t6/7/8 18:1, trans6/7/8-C18:1</t>
+  </si>
+  <si>
+    <t>t9-C18:1, trans-9-C18:1, t9C18:1, t918:1, t9 18:1, trans9-C18:1</t>
+  </si>
+  <si>
+    <t>t10-C18:1, trans-10-C18:1, t10C18:1, t1018:1, t10 18:1, trans10-C18:1</t>
+  </si>
+  <si>
+    <t>t11-C18:1, trans-11-C18:1, t11C18:1, t1118:1, t11 18:1, trans11-C18:1</t>
+  </si>
+  <si>
+    <t>t12-C18:1, trans-12-C18:1, t12C18:1, t1218:1, t12 18:1, trans12-C18:1</t>
+  </si>
+  <si>
+    <t>c9/t13/14-C18:1, cis-9/trans-13/trans-14-C18:1, c9/t13/14C18:1, t13/14+c918:1, c9 + t13/14 18:1, c9 +t13/t14 18:1</t>
+  </si>
+  <si>
+    <t>c9/t12/13/14-C18:1, cis-9/trans-12/13/14-C18:1, c9/t12/13/14C18:1, t12/13/14+c918:1, c9 + t12/13/14 18:1</t>
+  </si>
+  <si>
+    <t>t15-C18:1, trans-15-C18:1, t15C18:1, t1518:1, t15 18:1, trans15-C18:1</t>
+  </si>
+  <si>
+    <t>c11-C18:1, cis-11-C18:1, c11C18:1, c1118:1, c11 18:1</t>
+  </si>
+  <si>
+    <t>c12-C18:1, cis-12-C18:1, c12C18:1, c1218:1, c12 18:1</t>
+  </si>
+  <si>
+    <t>c13-C18:1, cis-13-C18:1, c13C18:1, c1318:1, c13 18:1</t>
+  </si>
+  <si>
+    <t>c14/t16-C18:1, cis-14/trans-16-C18:1, c14+t16C18:1, c14+t1618:1, c14/t16C18:1, c14+t16 18:1</t>
+  </si>
+  <si>
+    <t>c15-C18:1, cis-15-C18:1, c15C18:1, c1518:1, c15 18:1</t>
+  </si>
+  <si>
+    <t>CLA (c9,t11), CLA c9,t11, cis-9 trans-11 CLA, CLAc9t11C18:2, CLAc9t1118:2, CLA c9t11 18:2, c9t11-CLA</t>
+  </si>
+  <si>
+    <t>t11,c15-C18:2, trans-11 cis-15-C18:2, t11c15C18:2, t11c1518:2, t11,c15 18:2</t>
+  </si>
+  <si>
+    <t>C18:2n-6, C18:2 n-6, 18:2n-6, 18:2 n-6, n-6C18:2, n-618:2, n-6 18:2</t>
+  </si>
+  <si>
+    <t>C18:3n-6, C18:3 n-6, 18:3n-6, 18:3 n-6, n-6C18:3, n-618:3, n-6 18:3</t>
+  </si>
+  <si>
+    <t>C18:3n-3, C18:3 n-3, 18:3n-3, 18:3 n-3, n-3C18:3, n-318:3, n-3 18:3</t>
+  </si>
+  <si>
+    <t>c7-C20:1, cis-7-C20:1, c7C20:1, c720:1, c7 20:1</t>
+  </si>
+  <si>
+    <t>c9-C20:1, cis-9-C20:1, c9C20:1, c920:1, c9 20:1</t>
+  </si>
+  <si>
+    <t>CLA (t10,c12), CLA t10,c12, trans-10 cis-12 CLA, CLAt10c12C18:2, CLAt10c1218:2, CLA t10,c12 18:2, t10c12-CLA</t>
+  </si>
+  <si>
+    <t>C20:1 + CLA, C20:1+CLA, C20:1 + CLA (c9,t11), c7+c9 20:1 + CLAc9,t11 18:2</t>
+  </si>
+  <si>
+    <t>C20:1 + CLA, C20:1+CLA, C20:1 + CLA (c9,t11), c7 20:1 + CLAc9,t11 18:2</t>
+  </si>
+  <si>
+    <t>C20:3n-6, C20:3 n-6, 20:3n-6, 20:3 n-6, n-6C20:3, n-620:3, n-6 20:3</t>
+  </si>
+  <si>
+    <t>C20:3n-3, C20:3 n-3, 20:3n-3, 20:3 n-3, n-3C20:3, n-320:3, n-3 20:3</t>
+  </si>
+  <si>
+    <t>C20:4n-6, C20:4 n-6, 20:4n-6, 20:4 n-6, n-6C20:4, n-620:4, n-6 20:4</t>
+  </si>
+  <si>
+    <t>C20:5n-3, C20:5 n-3, 20:5n-3, 20:5 n-3, n-3C20:5, n-320:5, n-3 20:5</t>
+  </si>
+  <si>
+    <t>C22:4n-6, C22:4 n-6, 22:4n-6, 22:4 n-6, n-6C22:4, n-622:4, n-6 22:4</t>
+  </si>
+  <si>
+    <t>C22:5n-6, C22:5 n-6, 22:5n-6, 22:5 n-6, n-6C22:5, n-622:5, n-6 22:5</t>
+  </si>
+  <si>
+    <t>C22:5n-3, C22:5 n-3, 22:5n-3, 22:5 n-3, n-3C22:5, n-322:5, n-3 22:5</t>
+  </si>
+  <si>
+    <t>C22:6n-3, C22:6 n-3, 22:6n-3, 22:6 n-3, n-3C22:6, n-322:6, n-3 22:6</t>
+  </si>
+  <si>
+    <t>SFA, saturated fatty acids, saturated fatty acid</t>
+  </si>
+  <si>
+    <t>MUFA, monounsaturated fatty acids, monounsaturated fatty acid</t>
+  </si>
+  <si>
+    <t>PUFA, polyunsaturated fatty acids, polyunsaturated fatty acid</t>
   </si>
 </sst>
 </file>
@@ -2350,8 +2359,8 @@
   <dimension ref="A1:DE74"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
@@ -2807,7 +2816,7 @@
         <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
         <v>211</v>
@@ -2818,7 +2827,7 @@
         <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
         <v>212</v>
@@ -2829,7 +2838,7 @@
         <v>139</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C12" t="s">
         <v>213</v>
@@ -2840,7 +2849,7 @@
         <v>141</v>
       </c>
       <c r="B13" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
         <v>214</v>
@@ -2851,7 +2860,7 @@
         <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C14" t="s">
         <v>215</v>
@@ -2862,7 +2871,7 @@
         <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C15" t="s">
         <v>216</v>
@@ -2873,7 +2882,7 @@
         <v>143</v>
       </c>
       <c r="B16" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
         <v>217</v>
@@ -2884,7 +2893,7 @@
         <v>146</v>
       </c>
       <c r="B17" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
         <v>218</v>
@@ -2895,7 +2904,7 @@
         <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
         <v>219</v>
@@ -2906,7 +2915,7 @@
         <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C19" t="s">
         <v>220</v>
@@ -2917,7 +2926,7 @@
         <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
         <v>221</v>
@@ -2928,7 +2937,7 @@
         <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C21" t="s">
         <v>222</v>
@@ -2939,7 +2948,7 @@
         <v>149</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C22" t="s">
         <v>223</v>
@@ -2950,7 +2959,7 @@
         <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C23" t="s">
         <v>224</v>
@@ -2961,7 +2970,7 @@
         <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
         <v>225</v>
@@ -2972,7 +2981,7 @@
         <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C25" t="s">
         <v>226</v>
@@ -2983,7 +2992,7 @@
         <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C26" t="s">
         <v>227</v>
@@ -2994,7 +3003,7 @@
         <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C27" t="s">
         <v>228</v>
@@ -3005,7 +3014,7 @@
         <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C28" t="s">
         <v>229</v>
@@ -3016,7 +3025,7 @@
         <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C29" t="s">
         <v>230</v>
@@ -3027,7 +3036,7 @@
         <v>159</v>
       </c>
       <c r="B30" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C30" t="s">
         <v>231</v>
@@ -3038,7 +3047,7 @@
         <v>160</v>
       </c>
       <c r="B31" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C31" t="s">
         <v>232</v>
@@ -3049,7 +3058,7 @@
         <v>161</v>
       </c>
       <c r="B32" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="C32" t="s">
         <v>233</v>
@@ -3060,7 +3069,7 @@
         <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C33" t="s">
         <v>234</v>
@@ -3071,7 +3080,7 @@
         <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C34" t="s">
         <v>235</v>
@@ -3082,7 +3091,7 @@
         <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
+        <v>308</v>
       </c>
       <c r="C35" t="s">
         <v>236</v>
@@ -3093,7 +3102,7 @@
         <v>163</v>
       </c>
       <c r="B36" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C36" t="s">
         <v>237</v>
@@ -3115,7 +3124,7 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C38" t="s">
         <v>239</v>
@@ -3126,7 +3135,7 @@
         <v>165</v>
       </c>
       <c r="B39" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C39" t="s">
         <v>240</v>
@@ -3137,7 +3146,7 @@
         <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C40" t="s">
         <v>241</v>
@@ -3148,7 +3157,7 @@
         <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C41" t="s">
         <v>242</v>
@@ -3159,7 +3168,7 @@
         <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C42" t="s">
         <v>243</v>
@@ -3170,7 +3179,7 @@
         <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C43" t="s">
         <v>244</v>
@@ -3181,7 +3190,7 @@
         <v>170</v>
       </c>
       <c r="B44" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C44" t="s">
         <v>245</v>
@@ -3192,7 +3201,7 @@
         <v>171</v>
       </c>
       <c r="B45" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C45" t="s">
         <v>246</v>
@@ -3203,7 +3212,7 @@
         <v>172</v>
       </c>
       <c r="B46" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C46" t="s">
         <v>247</v>
@@ -3214,7 +3223,7 @@
         <v>173</v>
       </c>
       <c r="B47" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C47" t="s">
         <v>248</v>
@@ -3225,7 +3234,7 @@
         <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C48" t="s">
         <v>249</v>
@@ -3236,7 +3245,7 @@
         <v>175</v>
       </c>
       <c r="B49" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C49" t="s">
         <v>250</v>
@@ -3247,7 +3256,7 @@
         <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C50" t="s">
         <v>251</v>
@@ -3258,7 +3267,7 @@
         <v>177</v>
       </c>
       <c r="B51" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C51" t="s">
         <v>252</v>
@@ -3269,7 +3278,7 @@
         <v>178</v>
       </c>
       <c r="B52" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C52" t="s">
         <v>253</v>
@@ -3280,7 +3289,7 @@
         <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C53" t="s">
         <v>254</v>
@@ -3291,7 +3300,7 @@
         <v>180</v>
       </c>
       <c r="B54" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C54" t="s">
         <v>261</v>
@@ -3302,7 +3311,7 @@
         <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C55" t="s">
         <v>262</v>
@@ -3313,7 +3322,7 @@
         <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C56" t="s">
         <v>263</v>
@@ -3324,7 +3333,7 @@
         <v>182</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="C57" t="s">
         <v>255</v>
@@ -3335,7 +3344,7 @@
         <v>184</v>
       </c>
       <c r="B58" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C58" t="s">
         <v>256</v>
@@ -3346,7 +3355,7 @@
         <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C59" t="s">
         <v>257</v>
@@ -3357,7 +3366,7 @@
         <v>186</v>
       </c>
       <c r="B60" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s">
         <v>258</v>
@@ -3368,7 +3377,7 @@
         <v>187</v>
       </c>
       <c r="B61" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="C61" t="s">
         <v>259</v>
@@ -3379,7 +3388,7 @@
         <v>188</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="C62" t="s">
         <v>259</v>
@@ -3390,7 +3399,7 @@
         <v>189</v>
       </c>
       <c r="B63" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C63" t="s">
         <v>264</v>
@@ -3401,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="B64" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C64" t="s">
         <v>265</v>
@@ -3412,7 +3421,7 @@
         <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C65" t="s">
         <v>266</v>
@@ -3423,7 +3432,7 @@
         <v>193</v>
       </c>
       <c r="B66" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C66" t="s">
         <v>267</v>
@@ -3434,7 +3443,7 @@
         <v>190</v>
       </c>
       <c r="B67" t="s">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="C67" t="s">
         <v>260</v>
@@ -3445,7 +3454,7 @@
         <v>194</v>
       </c>
       <c r="B68" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C68" t="s">
         <v>268</v>
@@ -3456,7 +3465,7 @@
         <v>195</v>
       </c>
       <c r="B69" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C69" t="s">
         <v>269</v>
@@ -3467,7 +3476,7 @@
         <v>196</v>
       </c>
       <c r="B70" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C70" t="s">
         <v>270</v>
@@ -3478,7 +3487,7 @@
         <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C71" t="s">
         <v>271</v>
@@ -3489,7 +3498,7 @@
         <v>198</v>
       </c>
       <c r="B72" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C72" t="s">
         <v>199</v>
@@ -3500,7 +3509,7 @@
         <v>200</v>
       </c>
       <c r="B73" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C73" t="s">
         <v>201</v>
@@ -3511,7 +3520,7 @@
         <v>202</v>
       </c>
       <c r="B74" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C74" t="s">
         <v>203</v>

--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943AA0AF-A399-4B96-AC52-B734344EA122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2E75CC-3102-409D-B811-D75F3A3AACB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="349">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -974,9 +974,6 @@
     <t>iso-C18:0, iso-C18.0, isoC18:0, iso18:0, iso-18:0, iso 18:0</t>
   </si>
   <si>
-    <t>t6/7/8-C18:1, trans-6/7/8-C18:1, t6/7/8C18:1, t6/7/8 18:1, trans6/7/8-C18:1</t>
-  </si>
-  <si>
     <t>t9-C18:1, trans-9-C18:1, t9C18:1, t918:1, t9 18:1, trans9-C18:1</t>
   </si>
   <si>
@@ -1074,6 +1071,21 @@
   </si>
   <si>
     <t>PUFA, polyunsaturated fatty acids, polyunsaturated fatty acid</t>
+  </si>
+  <si>
+    <t>t6/7/8-C18:1, trans-6/7/8-C18:1, t6/7/8C18:1, t6/7/8 18:1, trans6/7/8-C18:1, t6/7/818:1</t>
+  </si>
+  <si>
+    <t>c24_0</t>
+  </si>
+  <si>
+    <t>C24:0</t>
+  </si>
+  <si>
+    <t>C24:1</t>
+  </si>
+  <si>
+    <t>c24_1</t>
   </si>
 </sst>
 </file>
@@ -2356,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE468F5-6397-4C82-931F-B2CE02F46428}">
-  <dimension ref="A1:DE74"/>
+  <dimension ref="A1:DE76"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
@@ -3135,7 +3147,7 @@
         <v>165</v>
       </c>
       <c r="B39" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="C39" t="s">
         <v>240</v>
@@ -3146,7 +3158,7 @@
         <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C40" t="s">
         <v>241</v>
@@ -3157,7 +3169,7 @@
         <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C41" t="s">
         <v>242</v>
@@ -3168,7 +3180,7 @@
         <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C42" t="s">
         <v>243</v>
@@ -3179,7 +3191,7 @@
         <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C43" t="s">
         <v>244</v>
@@ -3190,7 +3202,7 @@
         <v>170</v>
       </c>
       <c r="B44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C44" t="s">
         <v>245</v>
@@ -3201,7 +3213,7 @@
         <v>171</v>
       </c>
       <c r="B45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C45" t="s">
         <v>246</v>
@@ -3212,7 +3224,7 @@
         <v>172</v>
       </c>
       <c r="B46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C46" t="s">
         <v>247</v>
@@ -3223,7 +3235,7 @@
         <v>173</v>
       </c>
       <c r="B47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C47" t="s">
         <v>248</v>
@@ -3234,7 +3246,7 @@
         <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s">
         <v>249</v>
@@ -3245,7 +3257,7 @@
         <v>175</v>
       </c>
       <c r="B49" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C49" t="s">
         <v>250</v>
@@ -3256,7 +3268,7 @@
         <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C50" t="s">
         <v>251</v>
@@ -3267,7 +3279,7 @@
         <v>177</v>
       </c>
       <c r="B51" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C51" t="s">
         <v>252</v>
@@ -3278,7 +3290,7 @@
         <v>178</v>
       </c>
       <c r="B52" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C52" t="s">
         <v>253</v>
@@ -3289,7 +3301,7 @@
         <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C53" t="s">
         <v>254</v>
@@ -3300,7 +3312,7 @@
         <v>180</v>
       </c>
       <c r="B54" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C54" t="s">
         <v>261</v>
@@ -3311,7 +3323,7 @@
         <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C55" t="s">
         <v>262</v>
@@ -3322,7 +3334,7 @@
         <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C56" t="s">
         <v>263</v>
@@ -3344,7 +3356,7 @@
         <v>184</v>
       </c>
       <c r="B58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C58" t="s">
         <v>256</v>
@@ -3355,7 +3367,7 @@
         <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
         <v>257</v>
@@ -3366,7 +3378,7 @@
         <v>186</v>
       </c>
       <c r="B60" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C60" t="s">
         <v>258</v>
@@ -3377,7 +3389,7 @@
         <v>187</v>
       </c>
       <c r="B61" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C61" t="s">
         <v>259</v>
@@ -3388,7 +3400,7 @@
         <v>188</v>
       </c>
       <c r="B62" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C62" t="s">
         <v>259</v>
@@ -3399,7 +3411,7 @@
         <v>189</v>
       </c>
       <c r="B63" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C63" t="s">
         <v>264</v>
@@ -3410,7 +3422,7 @@
         <v>191</v>
       </c>
       <c r="B64" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C64" t="s">
         <v>265</v>
@@ -3421,7 +3433,7 @@
         <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C65" t="s">
         <v>266</v>
@@ -3432,7 +3444,7 @@
         <v>193</v>
       </c>
       <c r="B66" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C66" t="s">
         <v>267</v>
@@ -3454,7 +3466,7 @@
         <v>194</v>
       </c>
       <c r="B68" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C68" t="s">
         <v>268</v>
@@ -3465,7 +3477,7 @@
         <v>195</v>
       </c>
       <c r="B69" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C69" t="s">
         <v>269</v>
@@ -3476,7 +3488,7 @@
         <v>196</v>
       </c>
       <c r="B70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C70" t="s">
         <v>270</v>
@@ -3487,7 +3499,7 @@
         <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C71" t="s">
         <v>271</v>
@@ -3495,40 +3507,57 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>198</v>
+        <v>345</v>
       </c>
       <c r="B72" t="s">
-        <v>342</v>
-      </c>
-      <c r="C72" t="s">
-        <v>199</v>
+        <v>346</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>200</v>
+        <v>348</v>
       </c>
       <c r="B73" t="s">
-        <v>343</v>
-      </c>
-      <c r="C73" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" t="s">
+        <v>341</v>
+      </c>
+      <c r="C74" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" t="s">
+        <v>342</v>
+      </c>
+      <c r="C75" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
         <v>202</v>
       </c>
-      <c r="B74" t="s">
-        <v>344</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="B76" t="s">
+        <v>343</v>
+      </c>
+      <c r="C76" t="s">
         <v>203</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">

--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2E75CC-3102-409D-B811-D75F3A3AACB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA4C997-6A61-4BB5-BB82-3691C5E79B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
   <sheets>
-    <sheet name="vocabulary" sheetId="1" r:id="rId1"/>
+    <sheet name="vocabulary" sheetId="3" r:id="rId1"/>
     <sheet name="description" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="346">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -51,15 +51,9 @@
     <t>attribute</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>qualitative</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -369,9 +363,6 @@
     <t>identifier</t>
   </si>
   <si>
-    <t>quantitative</t>
-  </si>
-  <si>
     <t>numeric</t>
   </si>
   <si>
@@ -379,9 +370,6 @@
   </si>
   <si>
     <t>g_per_100_g_fatty_acids</t>
-  </si>
-  <si>
-    <t>fatty acid C18:0 concentration</t>
   </si>
   <si>
     <t>deprecated_names</t>
@@ -416,12 +404,6 @@
 In some cases the synonym depends on the sample type. E.g. in lanupro_ontology a generic name is used for e.g. fatty acids independent of the sample type, while ATOL uses separate numbers for milk or meat.</t>
   </si>
   <si>
-    <t>data category</t>
-  </si>
-  <si>
-    <t>dtring or numeric</t>
-  </si>
-  <si>
     <t>default variable unit when no units are specified in the variable name</t>
   </si>
   <si>
@@ -1086,6 +1068,15 @@
   </si>
   <si>
     <t>c24_1</t>
+  </si>
+  <si>
+    <t>Format of the variable</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>fatty acid concentration</t>
   </si>
 </sst>
 </file>
@@ -2367,1211 +2358,1913 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE468F5-6397-4C82-931F-B2CE02F46428}">
-  <dimension ref="A1:DE76"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E034C6-174E-4BD8-87DA-20B5D61D5D37}">
+  <dimension ref="A1:BX108"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="95.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:109">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>140</v>
+      </c>
+      <c r="R1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T1" t="s">
+        <v>141</v>
+      </c>
+      <c r="U1" t="s">
+        <v>142</v>
+      </c>
+      <c r="V1" t="s">
+        <v>143</v>
+      </c>
+      <c r="W1" t="s">
+        <v>144</v>
+      </c>
+      <c r="X1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>172</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>173</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>174</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>175</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>177</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>176</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>178</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>179</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>180</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>181</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>185</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>186</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>187</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>184</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>188</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>189</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>190</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>191</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>339</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>342</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>192</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>194</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:76">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N2" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S2" t="s">
+        <v>108</v>
+      </c>
+      <c r="T2" t="s">
+        <v>108</v>
+      </c>
+      <c r="U2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:76">
+      <c r="A3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H3" t="s">
+        <v>273</v>
+      </c>
+      <c r="I3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K3" t="s">
+        <v>275</v>
+      </c>
+      <c r="L3" t="s">
+        <v>276</v>
+      </c>
+      <c r="M3" t="s">
+        <v>285</v>
+      </c>
+      <c r="N3" t="s">
+        <v>277</v>
+      </c>
+      <c r="O3" t="s">
+        <v>286</v>
+      </c>
+      <c r="P3" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>287</v>
+      </c>
+      <c r="R3" t="s">
+        <v>288</v>
+      </c>
+      <c r="S3" t="s">
+        <v>289</v>
+      </c>
+      <c r="T3" t="s">
+        <v>279</v>
+      </c>
+      <c r="U3" t="s">
+        <v>290</v>
+      </c>
+      <c r="V3" t="s">
+        <v>280</v>
+      </c>
+      <c r="W3" t="s">
+        <v>291</v>
+      </c>
+      <c r="X3" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>294</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>295</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>296</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>298</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>281</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>300</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>301</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>302</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>303</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>270</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>304</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>338</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>305</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>306</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>307</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>308</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>309</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>310</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>311</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>312</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>314</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>315</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>317</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>318</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>319</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>320</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>282</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>322</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>323</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>324</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>325</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>327</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>328</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>329</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>330</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>283</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>331</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>332</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>333</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>334</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>340</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>341</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>335</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>336</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:76">
+      <c r="A4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I4" t="s">
+        <v>204</v>
+      </c>
+      <c r="J4" t="s">
+        <v>205</v>
+      </c>
+      <c r="K4" t="s">
+        <v>206</v>
+      </c>
+      <c r="L4" t="s">
+        <v>207</v>
+      </c>
+      <c r="M4" t="s">
+        <v>208</v>
+      </c>
+      <c r="N4" t="s">
+        <v>209</v>
+      </c>
+      <c r="O4" t="s">
+        <v>210</v>
+      </c>
+      <c r="P4" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>212</v>
+      </c>
+      <c r="R4" t="s">
+        <v>213</v>
+      </c>
+      <c r="S4" t="s">
+        <v>214</v>
+      </c>
+      <c r="T4" t="s">
+        <v>215</v>
+      </c>
+      <c r="U4" t="s">
+        <v>216</v>
+      </c>
+      <c r="V4" t="s">
+        <v>217</v>
+      </c>
+      <c r="W4" t="s">
+        <v>218</v>
+      </c>
+      <c r="X4" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>225</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>231</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>233</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>234</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>235</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>237</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>241</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>242</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>243</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>244</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>245</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>246</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>247</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>248</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>255</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>256</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>257</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>249</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>250</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>252</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>253</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>253</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>259</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>260</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>261</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>254</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>262</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>263</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>264</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>265</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>193</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>195</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:76">
+      <c r="A5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:76">
+      <c r="A6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="7" spans="1:76" ht="43.2">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AJ7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AK7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AM7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AP7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AQ7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AS7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AT7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AU7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AV7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AW7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AX7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AY7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AZ7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BA7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BB7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BC7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BD7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BE7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BF7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BG7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BH7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BI7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BJ7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BK7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BL7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BM7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BN7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BO7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BP7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BQ7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BR7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BS7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BT7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BU7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BV7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BW7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BX7" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:76">
+      <c r="A8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" t="s">
+        <v>110</v>
+      </c>
+      <c r="O8" t="s">
+        <v>110</v>
+      </c>
+      <c r="P8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>110</v>
+      </c>
+      <c r="R8" t="s">
+        <v>110</v>
+      </c>
+      <c r="S8" t="s">
+        <v>110</v>
+      </c>
+      <c r="T8" t="s">
+        <v>110</v>
+      </c>
+      <c r="U8" t="s">
+        <v>110</v>
+      </c>
+      <c r="V8" t="s">
+        <v>110</v>
+      </c>
+      <c r="W8" t="s">
+        <v>110</v>
+      </c>
+      <c r="X8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>110</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:76">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:76">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:76">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="12" spans="1:76">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="13" spans="1:76">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="14" spans="1:76">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="15" spans="1:76">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="16" spans="1:76">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1" t="s">
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1" t="s">
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="1" t="s">
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="1" t="s">
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="1" t="s">
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="1" t="s">
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="1" t="s">
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="1" t="s">
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="1" t="s">
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="1" t="s">
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="1" t="s">
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="1" t="s">
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="1" t="s">
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="1" t="s">
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="1" t="s">
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="1" t="s">
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="1" t="s">
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="1" t="s">
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="1" t="s">
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="1" t="s">
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="1" t="s">
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="CV1" s="1" t="s">
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="CW1" s="1" t="s">
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CX1" s="1" t="s">
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="CY1" s="1" t="s">
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DA1" s="1" t="s">
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DB1" s="1" t="s">
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DC1" s="1" t="s">
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DD1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="DE1" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:109">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:109">
-      <c r="A3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:109">
-      <c r="A4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" t="s">
-        <v>274</v>
-      </c>
-      <c r="C4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:109">
-      <c r="A5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:109">
-      <c r="A6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:109">
-      <c r="A7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:109">
-      <c r="A8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="1:109">
-      <c r="A9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:109">
-      <c r="A10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" t="s">
-        <v>290</v>
-      </c>
-      <c r="C10" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="11" spans="1:109">
-      <c r="A11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:109">
-      <c r="A12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C12" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="1:109">
-      <c r="A13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" spans="1:109">
-      <c r="A14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" t="s">
-        <v>283</v>
-      </c>
-      <c r="C14" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:109">
-      <c r="A15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" t="s">
-        <v>292</v>
-      </c>
-      <c r="C15" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" spans="1:109">
-      <c r="A16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C17" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B18" t="s">
-        <v>294</v>
-      </c>
-      <c r="C18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B19" t="s">
-        <v>295</v>
-      </c>
-      <c r="C19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" t="s">
-        <v>296</v>
-      </c>
-      <c r="C21" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" t="s">
-        <v>286</v>
-      </c>
-      <c r="C22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" t="s">
-        <v>297</v>
-      </c>
-      <c r="C23" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" t="s">
-        <v>298</v>
-      </c>
-      <c r="C24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>153</v>
-      </c>
-      <c r="B26" t="s">
-        <v>300</v>
-      </c>
-      <c r="C26" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" t="s">
-        <v>301</v>
-      </c>
-      <c r="C27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" t="s">
-        <v>302</v>
-      </c>
-      <c r="C28" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>158</v>
-      </c>
-      <c r="B29" t="s">
-        <v>303</v>
-      </c>
-      <c r="C29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>159</v>
-      </c>
-      <c r="B30" t="s">
-        <v>304</v>
-      </c>
-      <c r="C30" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" t="s">
-        <v>305</v>
-      </c>
-      <c r="C31" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" t="s">
-        <v>287</v>
-      </c>
-      <c r="C32" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>154</v>
-      </c>
-      <c r="B33" t="s">
-        <v>306</v>
-      </c>
-      <c r="C33" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>157</v>
-      </c>
-      <c r="B34" t="s">
-        <v>307</v>
-      </c>
-      <c r="C34" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" t="s">
-        <v>308</v>
-      </c>
-      <c r="C35" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" t="s">
-        <v>309</v>
-      </c>
-      <c r="C36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" t="s">
-        <v>276</v>
-      </c>
-      <c r="C37" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>164</v>
-      </c>
-      <c r="B38" t="s">
-        <v>310</v>
-      </c>
-      <c r="C38" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>165</v>
-      </c>
-      <c r="B39" t="s">
-        <v>344</v>
-      </c>
-      <c r="C39" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>166</v>
-      </c>
-      <c r="B40" t="s">
-        <v>311</v>
-      </c>
-      <c r="C40" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" t="s">
-        <v>312</v>
-      </c>
-      <c r="C41" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>168</v>
-      </c>
-      <c r="B42" t="s">
-        <v>313</v>
-      </c>
-      <c r="C42" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>169</v>
-      </c>
-      <c r="B43" t="s">
-        <v>314</v>
-      </c>
-      <c r="C43" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>170</v>
-      </c>
-      <c r="B44" t="s">
-        <v>315</v>
-      </c>
-      <c r="C44" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B45" t="s">
-        <v>316</v>
-      </c>
-      <c r="C45" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>172</v>
-      </c>
-      <c r="B46" t="s">
-        <v>317</v>
-      </c>
-      <c r="C46" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>173</v>
-      </c>
-      <c r="B47" t="s">
-        <v>318</v>
-      </c>
-      <c r="C47" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48" t="s">
-        <v>319</v>
-      </c>
-      <c r="C48" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>175</v>
-      </c>
-      <c r="B49" t="s">
-        <v>320</v>
-      </c>
-      <c r="C49" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>176</v>
-      </c>
-      <c r="B50" t="s">
-        <v>321</v>
-      </c>
-      <c r="C50" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>177</v>
-      </c>
-      <c r="B51" t="s">
-        <v>322</v>
-      </c>
-      <c r="C51" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>178</v>
-      </c>
-      <c r="B52" t="s">
-        <v>323</v>
-      </c>
-      <c r="C52" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>179</v>
-      </c>
-      <c r="B53" t="s">
-        <v>324</v>
-      </c>
-      <c r="C53" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>180</v>
-      </c>
-      <c r="B54" t="s">
-        <v>325</v>
-      </c>
-      <c r="C54" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>181</v>
-      </c>
-      <c r="B55" t="s">
-        <v>326</v>
-      </c>
-      <c r="C55" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>183</v>
-      </c>
-      <c r="B56" t="s">
-        <v>327</v>
-      </c>
-      <c r="C56" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>182</v>
-      </c>
-      <c r="B57" t="s">
-        <v>288</v>
-      </c>
-      <c r="C57" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>184</v>
-      </c>
-      <c r="B58" t="s">
-        <v>328</v>
-      </c>
-      <c r="C58" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>185</v>
-      </c>
-      <c r="B59" t="s">
-        <v>329</v>
-      </c>
-      <c r="C59" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>186</v>
-      </c>
-      <c r="B60" t="s">
-        <v>330</v>
-      </c>
-      <c r="C60" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>187</v>
-      </c>
-      <c r="B61" t="s">
-        <v>331</v>
-      </c>
-      <c r="C61" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>188</v>
-      </c>
-      <c r="B62" t="s">
-        <v>332</v>
-      </c>
-      <c r="C62" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>189</v>
-      </c>
-      <c r="B63" t="s">
-        <v>333</v>
-      </c>
-      <c r="C63" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>191</v>
-      </c>
-      <c r="B64" t="s">
-        <v>334</v>
-      </c>
-      <c r="C64" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>192</v>
-      </c>
-      <c r="B65" t="s">
-        <v>335</v>
-      </c>
-      <c r="C65" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>193</v>
-      </c>
-      <c r="B66" t="s">
-        <v>336</v>
-      </c>
-      <c r="C66" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>190</v>
-      </c>
-      <c r="B67" t="s">
-        <v>289</v>
-      </c>
-      <c r="C67" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>194</v>
-      </c>
-      <c r="B68" t="s">
-        <v>337</v>
-      </c>
-      <c r="C68" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>195</v>
-      </c>
-      <c r="B69" t="s">
-        <v>338</v>
-      </c>
-      <c r="C69" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>196</v>
-      </c>
-      <c r="B70" t="s">
-        <v>339</v>
-      </c>
-      <c r="C70" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
-        <v>197</v>
-      </c>
-      <c r="B71" t="s">
-        <v>340</v>
-      </c>
-      <c r="C71" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>345</v>
-      </c>
-      <c r="B72" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>348</v>
-      </c>
-      <c r="B73" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>198</v>
-      </c>
-      <c r="B74" t="s">
-        <v>341</v>
-      </c>
-      <c r="C74" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>200</v>
-      </c>
-      <c r="B75" t="s">
-        <v>342</v>
-      </c>
-      <c r="C75" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>202</v>
-      </c>
-      <c r="B76" t="s">
-        <v>343</v>
-      </c>
-      <c r="C76" t="s">
-        <v>203</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2AA43B74-602F-42D3-8C41-9A5E92E4A78B}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DABA885D-21F5-4062-A6F1-3774E53F0C07}">
           <x14:formula1>
-            <xm:f>description!$E$7:$H$7</xm:f>
+            <xm:f>description!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{63FF082E-FE70-4372-A8CC-717DC18F28AE}">
-          <x14:formula1>
-            <xm:f>description!$E$6:$H$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
+          <xm:sqref>B2:BX2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3581,13 +4274,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68D4BA7-81A7-496D-83F7-4CE2A3B40B1B}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="80.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3595,25 +4288,25 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3621,143 +4314,102 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>121</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="57.6">
+      <c r="C3" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>123</v>
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="57.6">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="57.6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>110</v>
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>111</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>128</v>
+      <c r="C8" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>129</v>
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
